--- a/InputData/ctrl-settings/BAEPAbCiPC/Bool Are Energy Prices Affected by Chng in Production Costs.xlsx
+++ b/InputData/ctrl-settings/BAEPAbCiPC/Bool Are Energy Prices Affected by Chng in Production Costs.xlsx
@@ -1,42 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ctrl-settings\BAEPAbCiPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\ctrl-settings\BAEPAbCiPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEA0A00-D6A6-4D26-8247-961C9C80FF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821543C2-567D-4203-BA9D-917EA0EB3665}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3555" yWindow="435" windowWidth="23595" windowHeight="16230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BAEPAbCiPC" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Source:</t>
   </si>
@@ -113,6 +103,15 @@
     <t>heat</t>
   </si>
   <si>
+    <t>As of EPS 3.1.0, this lever supports the three energy carriers (electricity,</t>
+  </si>
+  <si>
+    <t>district heat, and hydrogen), as well as fuels produced by the natural gas</t>
+  </si>
+  <si>
+    <t>and petroleum, coal, biomass, and biofuel industries, as noted on the blue tab.</t>
+  </si>
+  <si>
     <t>municipal solid waste (NOT USED)</t>
   </si>
   <si>
@@ -122,7 +121,16 @@
     <t>Unit: boolean (1 or 0)</t>
   </si>
   <si>
-    <t>We use it only for the fuel types that are energy carriers within the EPS.</t>
+    <t>In the U.S. model, by default, we allow the suppliers of energy carriers</t>
+  </si>
+  <si>
+    <t>(electricity, district heat, and hydrogen) to pass through changes in their</t>
+  </si>
+  <si>
+    <t>expenses, while other fuel suppliers do not, due to the influence of a global</t>
+  </si>
+  <si>
+    <t>market on setting prices.</t>
   </si>
 </sst>
 </file>
@@ -180,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -188,6 +196,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -501,7 +510,37 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -523,15 +562,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>1</v>
       </c>
     </row>
@@ -553,7 +592,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
@@ -632,10 +671,10 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="5">
         <v>1</v>
       </c>
     </row>
@@ -681,22 +720,193 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B21" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B22">
-        <v>0</v>
+      <c r="B22" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24C1FBD3-C019-492F-A43C-2885D2109A00}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E848B99-7829-4090-BD92-234699C73622}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCD6B45-6A66-48E4-A780-F2CD3D31C058}"/>
 </file>